--- a/plc/s7-1x00/core/hmi/EHmiCommand-v1.1.xlsx
+++ b/plc/s7-1x00/core/hmi/EHmiCommand-v1.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\hmi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5123B942-E51A-413A-94A5-AFC4ED8D6BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2540ADE4-F7EE-4AF2-B85E-0C3BD4A53949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -559,14 +559,14 @@
     <t>Bool</t>
   </si>
   <si>
-    <t>{"version":"v1.1","author":"cyanezf","family":"core/hmi"}</t>
+    <t>{"version":"v1.1","author":"cyanezf","family":"core/hmi","status":"current","deprecatedBy":null,"dependencies":[]}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -929,7 +929,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E59"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.54296875" bestFit="1" customWidth="1"/>
@@ -938,7 +938,7 @@
     <col min="5" max="5" width="101.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -955,7 +955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>177</v>
       </c>
@@ -972,7 +972,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>73</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>88</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>97</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>100</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>103</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>106</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>109</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>112</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>118</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>121</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>124</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>127</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>130</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>133</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>139</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>142</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>145</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>148</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>151</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>154</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>157</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>160</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>169</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>172</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>175</v>
       </c>
